--- a/backend/data/financials_by_company/000852.SZ.xlsx
+++ b/backend/data/financials_by_company/000852.SZ.xlsx
@@ -4132,10 +4132,8 @@
           <t>Wuhan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>430205</t>
-        </is>
+      <c r="D2" t="n">
+        <v>430205</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4348,7 +4346,7 @@
         <v>-1386068</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>0.25</v>
@@ -4595,7 +4593,7 @@
         <v>1679995231</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
         <v>0.25</v>
